--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104578_W14.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104578_W14.xlsx
@@ -565,73 +565,73 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.6214</v>
+        <v>5.7881</v>
       </c>
       <c r="E2" t="n">
-        <v>4.2469</v>
+        <v>5.0922</v>
       </c>
       <c r="F2" t="n">
-        <v>0.3745</v>
+        <v>0.6959</v>
       </c>
       <c r="G2" t="n">
-        <v>5.7102</v>
+        <v>5.7111</v>
       </c>
       <c r="H2" t="n">
-        <v>2.6075</v>
+        <v>2.6051</v>
       </c>
       <c r="I2" t="n">
-        <v>3.1027</v>
+        <v>3.106</v>
       </c>
       <c r="J2" t="n">
-        <v>5.1945</v>
+        <v>5.16</v>
       </c>
       <c r="K2" t="n">
-        <v>2.625</v>
+        <v>2.606</v>
       </c>
       <c r="L2" t="n">
-        <v>2.5694</v>
+        <v>2.554</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5157</v>
+        <v>0.5511</v>
       </c>
       <c r="N2" t="n">
-        <v>-0.0176</v>
+        <v>-0.0009</v>
       </c>
       <c r="O2" t="n">
-        <v>0.5333</v>
+        <v>0.552</v>
       </c>
       <c r="P2" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="Q2" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R2" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S2" t="n">
-        <v>-2.5009</v>
+        <v>-1.3296</v>
       </c>
       <c r="T2" t="n">
-        <v>-1.0253</v>
+        <v>-0.1282</v>
       </c>
       <c r="U2" t="n">
-        <v>-1.4756</v>
+        <v>-1.2014</v>
       </c>
       <c r="V2" t="n">
-        <v>1.639</v>
+        <v>1.6342</v>
       </c>
       <c r="W2" t="n">
-        <v>2.3461</v>
+        <v>2.3367</v>
       </c>
       <c r="X2" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>P. PELOS</t>
+          <t>L. LABEYRIE</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0809</v>
+        <v>2.7053</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3148</v>
+        <v>-0.1555</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.2339</v>
+        <v>2.8608</v>
       </c>
       <c r="G3" t="n">
-        <v>1.7675</v>
+        <v>1.3476</v>
       </c>
       <c r="H3" t="n">
-        <v>1.7808</v>
+        <v>2.1681</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.0133</v>
+        <v>-0.8205</v>
       </c>
       <c r="J3" t="n">
-        <v>1.3965</v>
+        <v>0.1956</v>
       </c>
       <c r="K3" t="n">
-        <v>1.2153</v>
+        <v>0.948</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1812</v>
+        <v>-0.7524</v>
       </c>
       <c r="M3" t="n">
-        <v>0.371</v>
+        <v>1.152</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5655</v>
+        <v>1.2201</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.1945</v>
+        <v>-0.06809999999999999</v>
       </c>
       <c r="P3" t="n">
-        <v>1.1342</v>
+        <v>2.0487</v>
       </c>
       <c r="Q3" t="n">
         <v>0</v>
       </c>
       <c r="R3" t="n">
-        <v>1.1342</v>
+        <v>2.0487</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.4313</v>
+        <v>-0.8487</v>
       </c>
       <c r="T3" t="n">
-        <v>0.8257</v>
+        <v>-0.5089</v>
       </c>
       <c r="U3" t="n">
-        <v>-1.257</v>
+        <v>-0.3399</v>
       </c>
       <c r="V3" t="n">
-        <v>0.6105</v>
+        <v>0.1578</v>
       </c>
       <c r="W3" t="n">
-        <v>1.0927</v>
+        <v>0.1578</v>
       </c>
       <c r="X3" t="n">
-        <v>-0.4822</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>M. TOBEY</t>
+          <t>P. PELOS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.9248</v>
+        <v>2.6289</v>
       </c>
       <c r="E4" t="n">
-        <v>2.8351</v>
+        <v>2.6463</v>
       </c>
       <c r="F4" t="n">
-        <v>0.0897</v>
+        <v>-0.0174</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.3339</v>
+        <v>1.7595</v>
       </c>
       <c r="H4" t="n">
-        <v>-1.2003</v>
+        <v>1.7698</v>
       </c>
       <c r="I4" t="n">
-        <v>0.8663999999999999</v>
+        <v>-0.0103</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.1377</v>
+        <v>1.3667</v>
       </c>
       <c r="K4" t="n">
-        <v>-0.884</v>
+        <v>1.1958</v>
       </c>
       <c r="L4" t="n">
-        <v>0.7463</v>
+        <v>0.1708</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.1962</v>
+        <v>0.3928</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3162</v>
+        <v>0.574</v>
       </c>
       <c r="O4" t="n">
-        <v>0.1201</v>
+        <v>-0.1811</v>
       </c>
       <c r="P4" t="n">
-        <v>2.0415</v>
+        <v>1.1382</v>
       </c>
       <c r="Q4" t="n">
         <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>2.0415</v>
+        <v>1.1382</v>
       </c>
       <c r="S4" t="n">
-        <v>0.6708</v>
+        <v>-0.8849</v>
       </c>
       <c r="T4" t="n">
-        <v>1.3338</v>
+        <v>0.1901</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.663</v>
+        <v>-1.075</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5463</v>
+        <v>0.6162</v>
       </c>
       <c r="W4" t="n">
-        <v>1.639</v>
+        <v>1.0895</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.0927</v>
+        <v>-0.4733</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>L. LABEYRIE</t>
+          <t>M. TOBEY</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>2.7885</v>
+        <v>1.6823</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.3315</v>
+        <v>1.81</v>
       </c>
       <c r="F5" t="n">
-        <v>3.12</v>
+        <v>-0.1277</v>
       </c>
       <c r="G5" t="n">
-        <v>1.3366</v>
+        <v>-0.3374</v>
       </c>
       <c r="H5" t="n">
-        <v>2.1629</v>
+        <v>-1.2169</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.8263</v>
+        <v>0.8794999999999999</v>
       </c>
       <c r="J5" t="n">
-        <v>0.2034</v>
+        <v>-0.1698</v>
       </c>
       <c r="K5" t="n">
-        <v>0.9524</v>
+        <v>-0.9145</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.749</v>
+        <v>0.7447</v>
       </c>
       <c r="M5" t="n">
-        <v>1.1333</v>
+        <v>-0.1676</v>
       </c>
       <c r="N5" t="n">
-        <v>1.2105</v>
+        <v>-0.3023</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.0772</v>
+        <v>0.1347</v>
       </c>
       <c r="P5" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7504</v>
+        <v>-0.5737</v>
       </c>
       <c r="T5" t="n">
-        <v>-0.6956</v>
+        <v>0.3456</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.0548</v>
+        <v>-0.9193</v>
       </c>
       <c r="V5" t="n">
-        <v>0.1607</v>
+        <v>0.5447</v>
       </c>
       <c r="W5" t="n">
-        <v>0.1607</v>
+        <v>1.6342</v>
       </c>
       <c r="X5" t="n">
-        <v>0</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="6">
@@ -877,64 +877,64 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>0.6870000000000001</v>
+        <v>0.6241</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.5523</v>
+        <v>-1.2614</v>
       </c>
       <c r="F6" t="n">
-        <v>2.2392</v>
+        <v>1.8855</v>
       </c>
       <c r="G6" t="n">
-        <v>0.9733000000000001</v>
+        <v>0.9864000000000001</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.0477</v>
+        <v>-0.0433</v>
       </c>
       <c r="I6" t="n">
-        <v>1.021</v>
+        <v>1.0297</v>
       </c>
       <c r="J6" t="n">
-        <v>0.1168</v>
+        <v>0.1094</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0795</v>
+        <v>0.0722</v>
       </c>
       <c r="L6" t="n">
-        <v>0.0373</v>
+        <v>0.0372</v>
       </c>
       <c r="M6" t="n">
-        <v>0.8565</v>
+        <v>0.877</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.1272</v>
+        <v>-0.1155</v>
       </c>
       <c r="O6" t="n">
-        <v>0.9837</v>
+        <v>0.9925</v>
       </c>
       <c r="P6" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q6" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.9006999999999999</v>
+        <v>-0.9754</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.6956</v>
+        <v>-0.3904</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.2051</v>
+        <v>-0.5849</v>
       </c>
       <c r="V6" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="W6" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X6" t="n">
         <v>0</v>
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.1345</v>
+        <v>0.2517</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.6668</v>
+        <v>-2.1581</v>
       </c>
       <c r="F7" t="n">
-        <v>2.5322</v>
+        <v>2.4098</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.944</v>
+        <v>-0.9419999999999999</v>
       </c>
       <c r="H7" t="n">
-        <v>0.0448</v>
+        <v>0.0377</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.9888</v>
+        <v>-0.9798</v>
       </c>
       <c r="J7" t="n">
-        <v>-1.7391</v>
+        <v>-1.7653</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.3157</v>
+        <v>-0.335</v>
       </c>
       <c r="L7" t="n">
-        <v>-1.4234</v>
+        <v>-1.4303</v>
       </c>
       <c r="M7" t="n">
-        <v>0.7952</v>
+        <v>0.8233</v>
       </c>
       <c r="N7" t="n">
-        <v>0.3605</v>
+        <v>0.3727</v>
       </c>
       <c r="O7" t="n">
-        <v>0.4346</v>
+        <v>0.4506</v>
       </c>
       <c r="P7" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R7" t="n">
-        <v>2.0415</v>
+        <v>2.0487</v>
       </c>
       <c r="S7" t="n">
-        <v>-1.8011</v>
+        <v>-1.4225</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.8861</v>
+        <v>-0.3441</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.9149</v>
+        <v>-1.0783</v>
       </c>
       <c r="V7" t="n">
-        <v>1.7032</v>
+        <v>1.7057</v>
       </c>
       <c r="W7" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X7" t="n">
-        <v>0.6105</v>
+        <v>0.6162</v>
       </c>
     </row>
     <row r="8">
@@ -1033,58 +1033,58 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.5165</v>
+        <v>-0.2954</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3898</v>
+        <v>-0.2096</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.1267</v>
+        <v>-0.0858</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.6251</v>
+        <v>-0.6241</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.1933</v>
+        <v>-0.1952</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.4318</v>
+        <v>-0.4289</v>
       </c>
       <c r="J8" t="n">
-        <v>0.0275</v>
+        <v>0.0205</v>
       </c>
       <c r="K8" t="n">
-        <v>0.0275</v>
+        <v>0.0205</v>
       </c>
       <c r="L8" t="n">
         <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.6526</v>
+        <v>-0.6446</v>
       </c>
       <c r="N8" t="n">
-        <v>-0.2209</v>
+        <v>-0.2157</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.4318</v>
+        <v>-0.4289</v>
       </c>
       <c r="P8" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7988</v>
+        <v>-0.5819</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.4174</v>
+        <v>-0.2301</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.3814</v>
+        <v>-0.3518</v>
       </c>
       <c r="V8" t="n">
         <v>0</v>
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9147999999999999</v>
+        <v>-1.0153</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4557</v>
+        <v>-0.7607</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.4591</v>
+        <v>-0.2546</v>
       </c>
       <c r="G9" t="n">
-        <v>1.5312</v>
+        <v>1.533</v>
       </c>
       <c r="H9" t="n">
-        <v>0.3637</v>
+        <v>0.362</v>
       </c>
       <c r="I9" t="n">
-        <v>1.1675</v>
+        <v>1.171</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2134</v>
+        <v>1.2023</v>
       </c>
       <c r="K9" t="n">
-        <v>0.6163</v>
+        <v>0.6065</v>
       </c>
       <c r="L9" t="n">
-        <v>0.5971</v>
+        <v>0.5958</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3178</v>
+        <v>0.3306</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.2526</v>
+        <v>-0.2446</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5705</v>
+        <v>0.5752</v>
       </c>
       <c r="P9" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R9" t="n">
-        <v>0.9073</v>
+        <v>0.9105</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.153</v>
+        <v>-0.2508</v>
       </c>
       <c r="T9" t="n">
-        <v>0.4386</v>
+        <v>0.1555</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.5916</v>
+        <v>-0.4063</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.9320000000000001</v>
+        <v>-0.9317</v>
       </c>
       <c r="W9" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X9" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="10">
@@ -1189,58 +1189,58 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.6322</v>
+        <v>-1.3006</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9529</v>
+        <v>-0.6022</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.6793</v>
+        <v>-0.6984</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.2786</v>
+        <v>-1.2692</v>
       </c>
       <c r="H10" t="n">
-        <v>-1.0174</v>
+        <v>-1.0086</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2612</v>
+        <v>-0.2607</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.6051</v>
+        <v>-0.609</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0693</v>
+        <v>0.0689</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6744</v>
+        <v>-0.6778999999999999</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.6735</v>
+        <v>-0.6603</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0867</v>
+        <v>-1.0775</v>
       </c>
       <c r="O10" t="n">
-        <v>0.4132</v>
+        <v>0.4173</v>
       </c>
       <c r="P10" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q10" t="n">
         <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.5804</v>
+        <v>-0.2589</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.3478</v>
+        <v>0.0068</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.2326</v>
+        <v>-0.2658</v>
       </c>
       <c r="V10" t="n">
         <v>0</v>
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.664</v>
+        <v>-2.3403</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.7127</v>
+        <v>-2.3854</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0487</v>
+        <v>0.0451</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.4117</v>
+        <v>-0.4152</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.1025</v>
+        <v>-0.1006</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.3092</v>
+        <v>-0.3145</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.706</v>
+        <v>-0.7329</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.1008</v>
+        <v>-0.1142</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6052</v>
+        <v>-0.6188</v>
       </c>
       <c r="M11" t="n">
-        <v>0.2943</v>
+        <v>0.3178</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.0017</v>
+        <v>0.0135</v>
       </c>
       <c r="O11" t="n">
-        <v>0.2959</v>
+        <v>0.3043</v>
       </c>
       <c r="P11" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q11" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R11" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="S11" t="n">
-        <v>0.2241</v>
+        <v>-0.4471</v>
       </c>
       <c r="T11" t="n">
-        <v>0.738</v>
+        <v>0.1019</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.5139</v>
+        <v>-0.549</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.7032</v>
+        <v>-1.7057</v>
       </c>
       <c r="W11" t="n">
-        <v>-0.6105</v>
+        <v>-0.6162</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.0927</v>
+        <v>-1.0895</v>
       </c>
     </row>
     <row r="12">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-5.4673</v>
+        <v>-4.2594</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.53</v>
+        <v>-3.7918</v>
       </c>
       <c r="F12" t="n">
-        <v>-0.9373</v>
+        <v>-0.4676</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.9165</v>
+        <v>-1.9192</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.0693</v>
+        <v>-0.0689</v>
       </c>
       <c r="I12" t="n">
-        <v>-1.8472</v>
+        <v>-1.8502</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.5362</v>
+        <v>-1.566</v>
       </c>
       <c r="K12" t="n">
-        <v>-0.2566</v>
+        <v>-0.2693</v>
       </c>
       <c r="L12" t="n">
-        <v>-1.2796</v>
+        <v>-1.2967</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.3803</v>
+        <v>-0.3532</v>
       </c>
       <c r="N12" t="n">
-        <v>0.1874</v>
+        <v>0.2003</v>
       </c>
       <c r="O12" t="n">
-        <v>-0.5676</v>
+        <v>-0.5535</v>
       </c>
       <c r="P12" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.2683</v>
+        <v>-2.2763</v>
       </c>
       <c r="R12" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S12" t="n">
-        <v>-2.324</v>
+        <v>-1.1126</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.8861</v>
+        <v>-0.1072</v>
       </c>
       <c r="U12" t="n">
-        <v>-1.4378</v>
+        <v>-1.0053</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.5463</v>
+        <v>-0.5447</v>
       </c>
       <c r="W12" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.7071</v>
+        <v>-0.7025</v>
       </c>
     </row>
     <row r="13">
@@ -1423,67 +1423,67 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.773300000000003</v>
+        <v>4.469399999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-2.1949</v>
+        <v>-1.776199999999999</v>
       </c>
       <c r="F13" t="n">
-        <v>5.968</v>
+        <v>6.2456</v>
       </c>
       <c r="G13" t="n">
-        <v>5.809</v>
+        <v>5.830500000000001</v>
       </c>
       <c r="H13" t="n">
-        <v>4.3292</v>
+        <v>4.3092</v>
       </c>
       <c r="I13" t="n">
-        <v>1.4798</v>
+        <v>1.5213</v>
       </c>
       <c r="J13" t="n">
-        <v>3.427999999999998</v>
+        <v>3.2115</v>
       </c>
       <c r="K13" t="n">
-        <v>4.028200000000001</v>
+        <v>3.8849</v>
       </c>
       <c r="L13" t="n">
-        <v>-0.6003000000000001</v>
+        <v>-0.6736</v>
       </c>
       <c r="M13" t="n">
-        <v>2.3812</v>
+        <v>2.6189</v>
       </c>
       <c r="N13" t="n">
-        <v>0.301</v>
+        <v>0.4240999999999999</v>
       </c>
       <c r="O13" t="n">
-        <v>2.0802</v>
+        <v>2.195</v>
       </c>
       <c r="P13" t="n">
-        <v>5.6708</v>
+        <v>5.6908</v>
       </c>
       <c r="Q13" t="n">
-        <v>-10.2075</v>
+        <v>-10.2435</v>
       </c>
       <c r="R13" t="n">
-        <v>15.8782</v>
+        <v>15.9342</v>
       </c>
       <c r="S13" t="n">
-        <v>-9.345700000000001</v>
+        <v>-8.6861</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.6178</v>
+        <v>-0.9089999999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>-7.7277</v>
+        <v>-7.777</v>
       </c>
       <c r="V13" t="n">
-        <v>1.6389</v>
+        <v>1.634299999999999</v>
       </c>
       <c r="W13" t="n">
-        <v>6.202800000000001</v>
+        <v>6.164899999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-4.563999999999999</v>
+        <v>-4.5306</v>
       </c>
     </row>
     <row r="14">
@@ -1501,64 +1501,64 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>3.3812</v>
+        <v>3.9504</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5571</v>
+        <v>2.1261</v>
       </c>
       <c r="F14" t="n">
-        <v>1.8241</v>
+        <v>1.8243</v>
       </c>
       <c r="G14" t="n">
-        <v>1.9283</v>
+        <v>1.9379</v>
       </c>
       <c r="H14" t="n">
-        <v>1.6031</v>
+        <v>1.6054</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3253</v>
+        <v>0.3325</v>
       </c>
       <c r="J14" t="n">
-        <v>2.1536</v>
+        <v>2.1372</v>
       </c>
       <c r="K14" t="n">
-        <v>2.7534</v>
+        <v>2.7407</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.5998</v>
+        <v>-0.6035</v>
       </c>
       <c r="M14" t="n">
-        <v>-0.2252</v>
+        <v>-0.1993</v>
       </c>
       <c r="N14" t="n">
-        <v>-1.1503</v>
+        <v>-1.1353</v>
       </c>
       <c r="O14" t="n">
-        <v>0.925</v>
+        <v>0.9360000000000001</v>
       </c>
       <c r="P14" t="n">
-        <v>0.4537</v>
+        <v>0.4553</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R14" t="n">
-        <v>1.8147</v>
+        <v>1.8211</v>
       </c>
       <c r="S14" t="n">
-        <v>0.2922</v>
+        <v>0.8547</v>
       </c>
       <c r="T14" t="n">
-        <v>0.0575</v>
+        <v>0.6522</v>
       </c>
       <c r="U14" t="n">
-        <v>0.2347</v>
+        <v>0.2025</v>
       </c>
       <c r="V14" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="W14" t="n">
-        <v>0.7071</v>
+        <v>0.7025</v>
       </c>
       <c r="X14" t="n">
         <v>0</v>
@@ -1579,73 +1579,73 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>2.5105</v>
+        <v>2.2683</v>
       </c>
       <c r="E15" t="n">
-        <v>0.6774</v>
+        <v>0.3082</v>
       </c>
       <c r="F15" t="n">
-        <v>1.8331</v>
+        <v>1.96</v>
       </c>
       <c r="G15" t="n">
-        <v>-1.5403</v>
+        <v>-1.5342</v>
       </c>
       <c r="H15" t="n">
-        <v>-2.1427</v>
+        <v>-2.1453</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6025</v>
+        <v>0.6111</v>
       </c>
       <c r="J15" t="n">
-        <v>-1.8186</v>
+        <v>-1.8375</v>
       </c>
       <c r="K15" t="n">
-        <v>-1.9679</v>
+        <v>-1.9865</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1493</v>
+        <v>0.1489</v>
       </c>
       <c r="M15" t="n">
-        <v>0.2784</v>
+        <v>0.3033</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.1749</v>
+        <v>-0.1588</v>
       </c>
       <c r="O15" t="n">
-        <v>0.4532</v>
+        <v>0.4622</v>
       </c>
       <c r="P15" t="n">
-        <v>1.361</v>
+        <v>1.3658</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2268</v>
+        <v>-0.2276</v>
       </c>
       <c r="R15" t="n">
-        <v>1.5878</v>
+        <v>1.5934</v>
       </c>
       <c r="S15" t="n">
-        <v>1.7578</v>
+        <v>1.505</v>
       </c>
       <c r="T15" t="n">
-        <v>1.6302</v>
+        <v>1.2839</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1276</v>
+        <v>0.2211</v>
       </c>
       <c r="V15" t="n">
-        <v>0.9320000000000001</v>
+        <v>0.9317</v>
       </c>
       <c r="W15" t="n">
-        <v>1.0927</v>
+        <v>1.0895</v>
       </c>
       <c r="X15" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>D. ENNIS</t>
+          <t>M. FORREST</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,67 +1657,67 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>2.1557</v>
+        <v>1.255</v>
       </c>
       <c r="E16" t="n">
-        <v>1.9855</v>
+        <v>0.1215</v>
       </c>
       <c r="F16" t="n">
-        <v>0.1702</v>
+        <v>1.1335</v>
       </c>
       <c r="G16" t="n">
-        <v>0.2924</v>
+        <v>0.4002</v>
       </c>
       <c r="H16" t="n">
-        <v>-1.9812</v>
+        <v>-0.5656</v>
       </c>
       <c r="I16" t="n">
-        <v>2.2736</v>
+        <v>0.9657</v>
       </c>
       <c r="J16" t="n">
-        <v>1.024</v>
+        <v>0.8023</v>
       </c>
       <c r="K16" t="n">
-        <v>-1.9159</v>
+        <v>0.8856000000000001</v>
       </c>
       <c r="L16" t="n">
-        <v>2.9399</v>
+        <v>-0.0832</v>
       </c>
       <c r="M16" t="n">
-        <v>-0.7316</v>
+        <v>-0.4022</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.0653</v>
+        <v>-1.4511</v>
       </c>
       <c r="O16" t="n">
-        <v>-0.6663</v>
+        <v>1.049</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.5878</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.4952</v>
+        <v>-2.2763</v>
       </c>
       <c r="R16" t="n">
-        <v>0.9073</v>
+        <v>1.5934</v>
       </c>
       <c r="S16" t="n">
-        <v>3.9009</v>
+        <v>0.4482</v>
       </c>
       <c r="T16" t="n">
-        <v>3.3602</v>
+        <v>0.506</v>
       </c>
       <c r="U16" t="n">
-        <v>0.5407</v>
+        <v>-0.0578</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.4498</v>
+        <v>1.0895</v>
       </c>
       <c r="W16" t="n">
-        <v>0.0965</v>
+        <v>1.0895</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.5463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
@@ -1735,58 +1735,58 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>1.4352</v>
+        <v>1.0898</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8263</v>
+        <v>0.3516</v>
       </c>
       <c r="F17" t="n">
-        <v>0.609</v>
+        <v>0.7382</v>
       </c>
       <c r="G17" t="n">
-        <v>0.3386</v>
+        <v>0.3372</v>
       </c>
       <c r="H17" t="n">
-        <v>-0.7675999999999999</v>
+        <v>-0.7696</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1062</v>
+        <v>1.1068</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.1173</v>
+        <v>-0.1221</v>
       </c>
       <c r="K17" t="n">
-        <v>-0.7517</v>
+        <v>-0.7552</v>
       </c>
       <c r="L17" t="n">
-        <v>0.6344</v>
+        <v>0.633</v>
       </c>
       <c r="M17" t="n">
-        <v>0.4559</v>
+        <v>0.4593</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.0159</v>
+        <v>-0.0144</v>
       </c>
       <c r="O17" t="n">
-        <v>0.4718</v>
+        <v>0.4738</v>
       </c>
       <c r="P17" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="Q17" t="n">
         <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S17" t="n">
-        <v>0.8698</v>
+        <v>0.525</v>
       </c>
       <c r="T17" t="n">
-        <v>0.9436</v>
+        <v>0.4738</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.0738</v>
+        <v>0.0512</v>
       </c>
       <c r="V17" t="n">
         <v>0</v>
@@ -1801,7 +1801,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>J. RADEBAUGH</t>
+          <t>D. ENNIS</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.3439</v>
+        <v>0.3976</v>
       </c>
       <c r="E18" t="n">
-        <v>-1.2034</v>
+        <v>0.2845</v>
       </c>
       <c r="F18" t="n">
-        <v>1.5473</v>
+        <v>0.1131</v>
       </c>
       <c r="G18" t="n">
-        <v>-0.2531</v>
+        <v>0.2848</v>
       </c>
       <c r="H18" t="n">
-        <v>-1.4472</v>
+        <v>-1.979</v>
       </c>
       <c r="I18" t="n">
-        <v>1.1941</v>
+        <v>2.2638</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.2991</v>
+        <v>0.984</v>
       </c>
       <c r="K18" t="n">
-        <v>-0.7069</v>
+        <v>-1.9348</v>
       </c>
       <c r="L18" t="n">
-        <v>0.4078</v>
+        <v>2.9187</v>
       </c>
       <c r="M18" t="n">
-        <v>0.046</v>
+        <v>-0.6992</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.7403999999999999</v>
+        <v>-0.0442</v>
       </c>
       <c r="O18" t="n">
-        <v>0.7864</v>
+        <v>-0.6549</v>
       </c>
       <c r="P18" t="n">
-        <v>0</v>
+        <v>-1.5934</v>
       </c>
       <c r="Q18" t="n">
-        <v>-1.1342</v>
+        <v>-2.5039</v>
       </c>
       <c r="R18" t="n">
-        <v>1.1342</v>
+        <v>0.9105</v>
       </c>
       <c r="S18" t="n">
-        <v>0.597</v>
+        <v>2.1647</v>
       </c>
       <c r="T18" t="n">
-        <v>0.2299</v>
+        <v>1.7182</v>
       </c>
       <c r="U18" t="n">
-        <v>0.3672</v>
+        <v>0.4465</v>
       </c>
       <c r="V18" t="n">
-        <v>0</v>
+        <v>-0.4584</v>
       </c>
       <c r="W18" t="n">
-        <v>0</v>
+        <v>0.0863</v>
       </c>
       <c r="X18" t="n">
-        <v>0</v>
+        <v>-0.5447</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. FORREST</t>
+          <t>J. RADEBAUGH</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,64 +1891,64 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.08160000000000001</v>
+        <v>0.3336</v>
       </c>
       <c r="E19" t="n">
-        <v>-1.0031</v>
+        <v>-1.1032</v>
       </c>
       <c r="F19" t="n">
-        <v>0.9215</v>
+        <v>1.4368</v>
       </c>
       <c r="G19" t="n">
-        <v>0.4275</v>
+        <v>-0.2587</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.5612</v>
+        <v>-1.4502</v>
       </c>
       <c r="I19" t="n">
-        <v>0.9887</v>
+        <v>1.1916</v>
       </c>
       <c r="J19" t="n">
-        <v>0.85</v>
+        <v>-0.3155</v>
       </c>
       <c r="K19" t="n">
-        <v>0.9036</v>
+        <v>-0.7174</v>
       </c>
       <c r="L19" t="n">
-        <v>-0.0536</v>
+        <v>0.4019</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.4225</v>
+        <v>0.0568</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.4648</v>
+        <v>-0.7328</v>
       </c>
       <c r="O19" t="n">
-        <v>1.0423</v>
+        <v>0.7896</v>
       </c>
       <c r="P19" t="n">
-        <v>-0.6805</v>
+        <v>0</v>
       </c>
       <c r="Q19" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R19" t="n">
-        <v>1.5878</v>
+        <v>1.1382</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.9212</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.6775</v>
+        <v>0.3505</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2438</v>
+        <v>0.2418</v>
       </c>
       <c r="V19" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="W19" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X19" t="n">
         <v>0</v>
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.2621</v>
+        <v>-0.9318</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.5145</v>
+        <v>-2.2306</v>
       </c>
       <c r="F20" t="n">
-        <v>1.2524</v>
+        <v>1.2988</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.7861</v>
+        <v>-0.7833</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1789</v>
+        <v>0.1836</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9649</v>
+        <v>-0.9668</v>
       </c>
       <c r="J20" t="n">
-        <v>-1.4661</v>
+        <v>-1.4731</v>
       </c>
       <c r="K20" t="n">
-        <v>0.0693</v>
+        <v>0.0689</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.5354</v>
+        <v>-1.542</v>
       </c>
       <c r="M20" t="n">
-        <v>0.68</v>
+        <v>0.6898</v>
       </c>
       <c r="N20" t="n">
-        <v>0.1096</v>
+        <v>0.1146</v>
       </c>
       <c r="O20" t="n">
-        <v>0.5705</v>
+        <v>0.5752</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.6805</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.361</v>
+        <v>-1.3658</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6805</v>
+        <v>0.6829</v>
       </c>
       <c r="S20" t="n">
-        <v>1.3652</v>
+        <v>0.6922</v>
       </c>
       <c r="T20" t="n">
-        <v>1.3126</v>
+        <v>0.6083</v>
       </c>
       <c r="U20" t="n">
-        <v>0.0526</v>
+        <v>0.0838</v>
       </c>
       <c r="V20" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
       <c r="W20" t="n">
         <v>0</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.1607</v>
+        <v>-0.1578</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>D. CACOK</t>
+          <t>T. NAKIC</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-1.2612</v>
+        <v>-1.1782</v>
       </c>
       <c r="E21" t="n">
-        <v>1.6078</v>
+        <v>-1.8845</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.869</v>
+        <v>0.7063</v>
       </c>
       <c r="G21" t="n">
-        <v>1.1338</v>
+        <v>-1.3674</v>
       </c>
       <c r="H21" t="n">
-        <v>1.8268</v>
+        <v>1.1684</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.6929999999999999</v>
+        <v>-2.5358</v>
       </c>
       <c r="J21" t="n">
-        <v>2.5536</v>
+        <v>-1.2548</v>
       </c>
       <c r="K21" t="n">
-        <v>2.4417</v>
+        <v>0.6378</v>
       </c>
       <c r="L21" t="n">
-        <v>0.112</v>
+        <v>-1.8925</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.4198</v>
+        <v>-0.1127</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.6149</v>
+        <v>0.5306</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.805</v>
+        <v>-0.6433</v>
       </c>
       <c r="P21" t="n">
-        <v>-2.0415</v>
+        <v>-0.6829</v>
       </c>
       <c r="Q21" t="n">
-        <v>-2.2683</v>
+        <v>-1.1382</v>
       </c>
       <c r="R21" t="n">
-        <v>0.2268</v>
+        <v>0.4553</v>
       </c>
       <c r="S21" t="n">
-        <v>0.3536</v>
+        <v>0.8721</v>
       </c>
       <c r="T21" t="n">
-        <v>0.2299</v>
+        <v>0.5084</v>
       </c>
       <c r="U21" t="n">
-        <v>0.1237</v>
+        <v>0.3637</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.7071</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>1.0927</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-1.7997</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>T. NAKIC</t>
+          <t>D. CACOK</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.452</v>
+        <v>-1.3459</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.983</v>
+        <v>1.4688</v>
       </c>
       <c r="F22" t="n">
-        <v>0.531</v>
+        <v>-2.8147</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.3658</v>
+        <v>1.1371</v>
       </c>
       <c r="H22" t="n">
-        <v>1.1585</v>
+        <v>1.8267</v>
       </c>
       <c r="I22" t="n">
-        <v>-2.5243</v>
+        <v>-0.6895</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.2359</v>
+        <v>2.5421</v>
       </c>
       <c r="K22" t="n">
-        <v>0.6407</v>
+        <v>2.4304</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.8767</v>
+        <v>0.1117</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.1299</v>
+        <v>-1.405</v>
       </c>
       <c r="N22" t="n">
-        <v>0.5178</v>
+        <v>-0.6037</v>
       </c>
       <c r="O22" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.8012</v>
       </c>
       <c r="P22" t="n">
-        <v>-0.6805</v>
+        <v>-2.0487</v>
       </c>
       <c r="Q22" t="n">
-        <v>-1.1342</v>
+        <v>-2.2763</v>
       </c>
       <c r="R22" t="n">
-        <v>0.4537</v>
+        <v>0.2276</v>
       </c>
       <c r="S22" t="n">
-        <v>0.5943000000000001</v>
+        <v>0.2682</v>
       </c>
       <c r="T22" t="n">
-        <v>0.3871</v>
+        <v>0.1136</v>
       </c>
       <c r="U22" t="n">
-        <v>0.2072</v>
+        <v>0.1546</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-0.7025</v>
       </c>
       <c r="W22" t="n">
-        <v>0</v>
+        <v>1.0895</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-1.792</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Z. HICKS</t>
+          <t>D. DEJULIUS</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.0587</v>
+        <v>-2.0584</v>
       </c>
       <c r="E23" t="n">
-        <v>-2.4714</v>
+        <v>-2.0241</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.5873</v>
+        <v>-0.0343</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.4342</v>
+        <v>-3.1504</v>
       </c>
       <c r="H23" t="n">
-        <v>-1.9784</v>
+        <v>0.1006</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.4558</v>
+        <v>-3.251</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.4461</v>
+        <v>-2.6669</v>
       </c>
       <c r="K23" t="n">
-        <v>-0.7344000000000001</v>
+        <v>-0.3867</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.7117</v>
+        <v>-2.2802</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.988</v>
+        <v>-0.4835</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.244</v>
+        <v>0.4873</v>
       </c>
       <c r="O23" t="n">
-        <v>0.2559</v>
+        <v>-0.9708</v>
       </c>
       <c r="P23" t="n">
-        <v>-1.8147</v>
+        <v>0.6829</v>
       </c>
       <c r="Q23" t="n">
-        <v>-2.2683</v>
+        <v>-0.2276</v>
       </c>
       <c r="R23" t="n">
-        <v>0.4537</v>
+        <v>0.9105</v>
       </c>
       <c r="S23" t="n">
-        <v>1.1901</v>
+        <v>0.7246</v>
       </c>
       <c r="T23" t="n">
-        <v>1.2431</v>
+        <v>0.7126</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.0529</v>
+        <v>0.0119</v>
       </c>
       <c r="V23" t="n">
-        <v>0</v>
+        <v>-0.3155</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.1578</v>
       </c>
       <c r="X23" t="n">
-        <v>0</v>
+        <v>-0.4733</v>
       </c>
     </row>
     <row r="24">
@@ -2281,73 +2281,73 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.538</v>
+        <v>-3.0364</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.3288</v>
+        <v>-0.5124</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.2092</v>
+        <v>-2.5239</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.4164</v>
+        <v>-0.4045</v>
       </c>
       <c r="H24" t="n">
-        <v>-0.3205</v>
+        <v>-0.3107</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.0959</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="J24" t="n">
-        <v>0.0439</v>
+        <v>0.0385</v>
       </c>
       <c r="K24" t="n">
-        <v>-0.6651</v>
+        <v>-0.669</v>
       </c>
       <c r="L24" t="n">
-        <v>0.709</v>
+        <v>0.7075</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.4603</v>
+        <v>-0.443</v>
       </c>
       <c r="N24" t="n">
-        <v>0.3446</v>
+        <v>0.3583</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.805</v>
+        <v>-0.8012</v>
       </c>
       <c r="P24" t="n">
-        <v>-0.9073</v>
+        <v>-0.9105</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.1342</v>
+        <v>-1.1382</v>
       </c>
       <c r="R24" t="n">
-        <v>0.2268</v>
+        <v>0.2276</v>
       </c>
       <c r="S24" t="n">
-        <v>0.5175</v>
+        <v>1.0023</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.3992</v>
+        <v>0.4294</v>
       </c>
       <c r="U24" t="n">
-        <v>0.9167</v>
+        <v>0.5729</v>
       </c>
       <c r="V24" t="n">
-        <v>-2.7317</v>
+        <v>-2.7237</v>
       </c>
       <c r="W24" t="n">
-        <v>0.1607</v>
+        <v>0.1578</v>
       </c>
       <c r="X24" t="n">
-        <v>-2.8924</v>
+        <v>-2.8814</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>D. DEJULIUS</t>
+          <t>Z. HICKS</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
@@ -2359,67 +2359,67 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.9462</v>
+        <v>-3.7266</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.2788</v>
+        <v>-3.3092</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.6674</v>
+        <v>-0.4174</v>
       </c>
       <c r="G25" t="n">
-        <v>-3.1336</v>
+        <v>-2.4292</v>
       </c>
       <c r="H25" t="n">
-        <v>0.1025</v>
+        <v>-1.9734</v>
       </c>
       <c r="I25" t="n">
-        <v>-3.2361</v>
+        <v>-0.4558</v>
       </c>
       <c r="J25" t="n">
-        <v>-2.6229</v>
+        <v>-1.4531</v>
       </c>
       <c r="K25" t="n">
-        <v>-0.3676</v>
+        <v>-0.7379</v>
       </c>
       <c r="L25" t="n">
-        <v>-2.2552</v>
+        <v>-0.7151999999999999</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.5107</v>
+        <v>-0.9761</v>
       </c>
       <c r="N25" t="n">
-        <v>0.4701</v>
+        <v>-1.2355</v>
       </c>
       <c r="O25" t="n">
-        <v>-0.9808</v>
+        <v>0.2593</v>
       </c>
       <c r="P25" t="n">
-        <v>0.6805</v>
+        <v>-1.8211</v>
       </c>
       <c r="Q25" t="n">
-        <v>-0.2268</v>
+        <v>-2.2763</v>
       </c>
       <c r="R25" t="n">
-        <v>0.9073</v>
+        <v>0.4553</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.1717</v>
+        <v>0.5236</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.5898</v>
+        <v>0.4202</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.5819</v>
+        <v>0.1035</v>
       </c>
       <c r="V25" t="n">
-        <v>-0.3214</v>
+        <v>0</v>
       </c>
       <c r="W25" t="n">
-        <v>0.1607</v>
+        <v>0</v>
       </c>
       <c r="X25" t="n">
-        <v>-0.4822</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -2437,67 +2437,67 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-3.773300000000001</v>
+        <v>-2.982599999999999</v>
       </c>
       <c r="E26" t="n">
-        <v>-6.1289</v>
+        <v>-6.4033</v>
       </c>
       <c r="F26" t="n">
-        <v>2.3557</v>
+        <v>3.4207</v>
       </c>
       <c r="G26" t="n">
-        <v>-5.8089</v>
+        <v>-5.8305</v>
       </c>
       <c r="H26" t="n">
-        <v>-4.329</v>
+        <v>-4.309099999999999</v>
       </c>
       <c r="I26" t="n">
-        <v>-1.4796</v>
+        <v>-1.5211</v>
       </c>
       <c r="J26" t="n">
-        <v>-2.3809</v>
+        <v>-2.6189</v>
       </c>
       <c r="K26" t="n">
-        <v>-0.3008000000000001</v>
+        <v>-0.4240999999999999</v>
       </c>
       <c r="L26" t="n">
-        <v>-2.08</v>
+        <v>-2.1949</v>
       </c>
       <c r="M26" t="n">
-        <v>-3.4277</v>
+        <v>-3.2118</v>
       </c>
       <c r="N26" t="n">
-        <v>-4.0284</v>
+        <v>-3.885</v>
       </c>
       <c r="O26" t="n">
-        <v>0.6002999999999997</v>
+        <v>0.6737000000000002</v>
       </c>
       <c r="P26" t="n">
-        <v>-5.6708</v>
+        <v>-5.690799999999999</v>
       </c>
       <c r="Q26" t="n">
-        <v>-15.8783</v>
+        <v>-15.9342</v>
       </c>
       <c r="R26" t="n">
-        <v>10.2074</v>
+        <v>10.2434</v>
       </c>
       <c r="S26" t="n">
-        <v>9.345499999999999</v>
+        <v>10.1728</v>
       </c>
       <c r="T26" t="n">
-        <v>7.727599999999999</v>
+        <v>7.777100000000001</v>
       </c>
       <c r="U26" t="n">
-        <v>1.618</v>
+        <v>2.3957</v>
       </c>
       <c r="V26" t="n">
-        <v>-1.6389</v>
+        <v>-1.6342</v>
       </c>
       <c r="W26" t="n">
-        <v>4.4031</v>
+        <v>4.3729</v>
       </c>
       <c r="X26" t="n">
-        <v>-6.042</v>
+        <v>-6.007</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104578_W14.xlsx
+++ b/informes_data/ACB/2025-26/Regular_Season/individual/NP_play_by_play_104578_W14.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X26"/>
+  <dimension ref="A1:Y26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_104578_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,6 +715,11 @@
       <c r="X3" t="n">
         <v>0</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_104578_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -783,6 +798,11 @@
       <c r="X4" t="n">
         <v>-0.4733</v>
       </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_104578_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -861,6 +881,11 @@
       <c r="X5" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_104578_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -939,6 +964,11 @@
       <c r="X6" t="n">
         <v>0</v>
       </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_104578_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -1017,6 +1047,11 @@
       <c r="X7" t="n">
         <v>0.6162</v>
       </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_104578_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1095,6 +1130,11 @@
       <c r="X8" t="n">
         <v>0</v>
       </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_104578_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1173,6 +1213,11 @@
       <c r="X9" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_104578_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1251,6 +1296,11 @@
       <c r="X10" t="n">
         <v>0</v>
       </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_104578_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1329,6 +1379,11 @@
       <c r="X11" t="n">
         <v>-1.0895</v>
       </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_104578_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1407,6 +1462,11 @@
       <c r="X12" t="n">
         <v>-0.7025</v>
       </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_104578_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1485,6 +1545,7 @@
       <c r="X13" t="n">
         <v>-4.5306</v>
       </c>
+      <c r="Y13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -1563,6 +1624,11 @@
       <c r="X14" t="n">
         <v>0</v>
       </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_104578_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -1641,6 +1707,11 @@
       <c r="X15" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>play_by_play_104578_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -1719,6 +1790,11 @@
       <c r="X16" t="n">
         <v>0</v>
       </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_104578_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -1797,6 +1873,11 @@
       <c r="X17" t="n">
         <v>0</v>
       </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_104578_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
@@ -1875,6 +1956,11 @@
       <c r="X18" t="n">
         <v>-0.5447</v>
       </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_104578_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -1953,6 +2039,11 @@
       <c r="X19" t="n">
         <v>0</v>
       </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_104578_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
@@ -2031,6 +2122,11 @@
       <c r="X20" t="n">
         <v>-0.1578</v>
       </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_104578_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -2109,6 +2205,11 @@
       <c r="X21" t="n">
         <v>0</v>
       </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_104578_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -2187,6 +2288,11 @@
       <c r="X22" t="n">
         <v>-1.792</v>
       </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_104578_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
@@ -2265,6 +2371,11 @@
       <c r="X23" t="n">
         <v>-0.4733</v>
       </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_104578_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
@@ -2343,6 +2454,11 @@
       <c r="X24" t="n">
         <v>-2.8814</v>
       </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_104578_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
@@ -2421,6 +2537,11 @@
       <c r="X25" t="n">
         <v>0</v>
       </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_104578_W14.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
@@ -2499,6 +2620,7 @@
       <c r="X26" t="n">
         <v>-6.007</v>
       </c>
+      <c r="Y26" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
